--- a/software_developer_forms/009_internet_of_things_survey--software_developer_forms.xlsx
+++ b/software_developer_forms/009_internet_of_things_survey--software_developer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>&lt;text&gt;</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -621,7 +621,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>&lt;text&gt;</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>&lt;text&gt;</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -667,7 +667,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>&lt;text&gt;</t>
+          <t>Contact Info</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,12 +685,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>contact_info_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>&lt;text&gt;</t>
+          <t>Contact Info 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -715,8 +715,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -744,12 +744,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'&lt;text&gt;',_'value':_'&lt;text&gt;'}</t>
+          <t>&lt;text&gt;</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '&lt;text&gt;', 'value': '&lt;text&gt;'}</t>
+          <t>&lt;text&gt;</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'home_automation',_'value':_'&lt;text&gt;'}</t>
+          <t>home_automation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Home Automation', 'value': '&lt;text&gt;'}</t>
+          <t>Home Automation</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'health_monitoring',_'value':_'&lt;text&gt;'}</t>
+          <t>health_monitoring</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Health Monitoring', 'value': '&lt;text&gt;'}</t>
+          <t>Health Monitoring</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'energy_management',_'value':_'&lt;text&gt;'}</t>
+          <t>energy_management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Energy Management', 'value': '&lt;text&gt;'}</t>
+          <t>Energy Management</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'&lt;text&gt;'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': '&lt;text&gt;'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
